--- a/VerveStacks_BRA_grids_kan10/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids_kan10/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6466622-8AA8-4740-99AC-63798F6060DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1C81D25-66E7-4DAD-B08A-5BE6B17F9C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0D373270-31AA-411A-A155-BDF806C492F8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CEBB5AA6-4D28-4D06-9046-F3B8C26F224A}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -2283,10 +2283,10 @@
     <t>CHP</t>
   </si>
   <si>
+    <t>Aggregated Plant -- operating -- CHP (captive)</t>
+  </si>
+  <si>
     <t>Aggregated Plant -- construction -- CHP</t>
-  </si>
-  <si>
-    <t>Aggregated Plant -- operating -- CHP (captive)</t>
   </si>
   <si>
     <t>Aggregated Plant -- operating -- CHP</t>
@@ -6191,7 +6191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57FD83D5-9B5F-4D71-8585-7B0DDECC7972}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56BCA14-8B19-484D-A8CB-F9CC62931882}">
   <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6578,7 +6578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7180581B-963E-483A-9E3B-E95985217230}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C236062-3FD3-4218-A0BC-15E4ECF3544D}">
   <dimension ref="B9:V141"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14780,7 +14780,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A5B0FE7-E8CF-4410-AE60-A38961AA4B6B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1751FC-A0D8-4A5C-A4EF-98869A42DC63}">
   <dimension ref="B9:W296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32229,7 +32229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A1F021A-3A7A-4580-9F57-209C276DA0E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8137856-6FBC-4A33-9C85-19BCD8FB8E2B}">
   <dimension ref="B9:W1247"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32828,7 +32828,7 @@
         <v>15</v>
       </c>
       <c r="S19" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="T19" t="s">
         <v>740</v>
@@ -32890,7 +32890,7 @@
         <v>15</v>
       </c>
       <c r="S20" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T20" t="s">
         <v>740</v>
@@ -33014,7 +33014,7 @@
         <v>15</v>
       </c>
       <c r="S22" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T22" t="s">
         <v>740</v>
@@ -33073,7 +33073,7 @@
         <v>15</v>
       </c>
       <c r="S23" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T23" t="s">
         <v>740</v>
@@ -33132,7 +33132,7 @@
         <v>15</v>
       </c>
       <c r="S24" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="T24" t="s">
         <v>740</v>
@@ -33191,7 +33191,7 @@
         <v>15</v>
       </c>
       <c r="S25" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="T25" t="s">
         <v>740</v>
@@ -33309,7 +33309,7 @@
         <v>15</v>
       </c>
       <c r="S27" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T27" t="s">
         <v>740</v>
@@ -33427,7 +33427,7 @@
         <v>15</v>
       </c>
       <c r="S29" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T29" t="s">
         <v>740</v>
@@ -33604,7 +33604,7 @@
         <v>15</v>
       </c>
       <c r="S32" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T32" t="s">
         <v>740</v>
@@ -33840,7 +33840,7 @@
         <v>15</v>
       </c>
       <c r="S36" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T36" t="s">
         <v>740</v>
@@ -33964,7 +33964,7 @@
         <v>15</v>
       </c>
       <c r="S38" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T38" t="s">
         <v>740</v>
@@ -34088,7 +34088,7 @@
         <v>15</v>
       </c>
       <c r="S40" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="T40" t="s">
         <v>740</v>
@@ -34150,7 +34150,7 @@
         <v>15</v>
       </c>
       <c r="S41" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T41" t="s">
         <v>740</v>
@@ -34398,7 +34398,7 @@
         <v>15</v>
       </c>
       <c r="S45" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="T45" t="s">
         <v>740</v>
@@ -34460,7 +34460,7 @@
         <v>15</v>
       </c>
       <c r="S46" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="T46" t="s">
         <v>740</v>
@@ -34646,7 +34646,7 @@
         <v>15</v>
       </c>
       <c r="S49" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T49" t="s">
         <v>740</v>
@@ -34950,7 +34950,7 @@
         <v>15</v>
       </c>
       <c r="S54" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T54" t="s">
         <v>740</v>
@@ -35186,7 +35186,7 @@
         <v>15</v>
       </c>
       <c r="S58" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T58" t="s">
         <v>740</v>
@@ -40568,7 +40568,7 @@
         <v>2021</v>
       </c>
       <c r="G148">
-        <v>3.0999999999999999E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="H148">
         <v>0.30719999999999997</v>
@@ -40627,7 +40627,7 @@
         <v>2021</v>
       </c>
       <c r="G149">
-        <v>2.8999999999999998E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="H149">
         <v>0.30719999999999997</v>
@@ -40804,7 +40804,7 @@
         <v>2028</v>
       </c>
       <c r="G152">
-        <v>8.5000000000000006E-3</v>
+        <v>0.02</v>
       </c>
       <c r="H152">
         <v>0.30719999999999997</v>
@@ -40863,7 +40863,7 @@
         <v>2028</v>
       </c>
       <c r="G153">
-        <v>0.02</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="H153">
         <v>0.30719999999999997</v>
@@ -41994,7 +41994,7 @@
         <v>15</v>
       </c>
       <c r="S171" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="T171" t="s">
         <v>740</v>
@@ -42056,7 +42056,7 @@
         <v>15</v>
       </c>
       <c r="S172" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T172" t="s">
         <v>740</v>
@@ -42236,7 +42236,7 @@
         <v>15</v>
       </c>
       <c r="S175" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T175" t="s">
         <v>740</v>
@@ -42478,7 +42478,7 @@
         <v>15</v>
       </c>
       <c r="S179" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T179" t="s">
         <v>740</v>
@@ -42664,7 +42664,7 @@
         <v>15</v>
       </c>
       <c r="S182" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T182" t="s">
         <v>740</v>
@@ -42850,7 +42850,7 @@
         <v>15</v>
       </c>
       <c r="S185" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="T185" t="s">
         <v>740</v>
@@ -42909,7 +42909,7 @@
         <v>15</v>
       </c>
       <c r="S186" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="T186" t="s">
         <v>740</v>
@@ -43027,7 +43027,7 @@
         <v>15</v>
       </c>
       <c r="S188" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T188" t="s">
         <v>740</v>
@@ -43151,7 +43151,7 @@
         <v>15</v>
       </c>
       <c r="S190" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T190" t="s">
         <v>740</v>
@@ -43213,7 +43213,7 @@
         <v>15</v>
       </c>
       <c r="S191" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T191" t="s">
         <v>740</v>
@@ -43275,7 +43275,7 @@
         <v>15</v>
       </c>
       <c r="S192" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T192" t="s">
         <v>740</v>
@@ -43334,7 +43334,7 @@
         <v>15</v>
       </c>
       <c r="S193" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T193" t="s">
         <v>740</v>
@@ -43396,7 +43396,7 @@
         <v>15</v>
       </c>
       <c r="S194" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="T194" t="s">
         <v>740</v>
@@ -43520,7 +43520,7 @@
         <v>15</v>
       </c>
       <c r="S196" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T196" t="s">
         <v>740</v>
@@ -43830,7 +43830,7 @@
         <v>15</v>
       </c>
       <c r="S201" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="T201" t="s">
         <v>740</v>
@@ -49981,10 +49981,10 @@
         <v>2010</v>
       </c>
       <c r="G302">
-        <v>3.7999999999999999E-2</v>
+        <v>0.125</v>
       </c>
       <c r="H302">
-        <v>0.26880000000000004</v>
+        <v>0.26880000000000009</v>
       </c>
       <c r="I302">
         <v>4016.25</v>
@@ -50043,10 +50043,10 @@
         <v>2010</v>
       </c>
       <c r="G303">
-        <v>0.125</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="H303">
-        <v>0.26880000000000009</v>
+        <v>0.26880000000000004</v>
       </c>
       <c r="I303">
         <v>4016.25</v>
@@ -50167,7 +50167,7 @@
         <v>2012</v>
       </c>
       <c r="G305">
-        <v>3.5999999999999999E-3</v>
+        <v>0.01</v>
       </c>
       <c r="H305">
         <v>0.28799999999999998</v>
@@ -50229,7 +50229,7 @@
         <v>2012</v>
       </c>
       <c r="G306">
-        <v>0.01</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="H306">
         <v>0.28799999999999998</v>
@@ -51073,16 +51073,16 @@
         <v>2015</v>
       </c>
       <c r="G320">
-        <v>1.83E-2</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="H320">
-        <v>0.28800000000000003</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="I320">
         <v>4016.25</v>
       </c>
       <c r="J320">
-        <v>152.10000000000002</v>
+        <v>152.1</v>
       </c>
       <c r="K320">
         <v>8.64</v>
@@ -51132,16 +51132,16 @@
         <v>2015</v>
       </c>
       <c r="G321">
-        <v>2.3999999999999998E-3</v>
+        <v>1.83E-2</v>
       </c>
       <c r="H321">
-        <v>0.28799999999999998</v>
+        <v>0.28800000000000003</v>
       </c>
       <c r="I321">
         <v>4016.25</v>
       </c>
       <c r="J321">
-        <v>152.1</v>
+        <v>152.10000000000002</v>
       </c>
       <c r="K321">
         <v>8.64</v>
@@ -51250,13 +51250,13 @@
         <v>2021</v>
       </c>
       <c r="G323">
-        <v>7.7000000000000002E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="H323">
         <v>0.30719999999999997</v>
       </c>
       <c r="I323">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="J323">
         <v>152.1</v>
@@ -51309,13 +51309,13 @@
         <v>2021</v>
       </c>
       <c r="G324">
-        <v>2.3E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="H324">
         <v>0.30719999999999997</v>
       </c>
       <c r="I324">
-        <v>4016.2500000000005</v>
+        <v>4016.25</v>
       </c>
       <c r="J324">
         <v>152.1</v>
@@ -51368,13 +51368,13 @@
         <v>2022</v>
       </c>
       <c r="G325">
-        <v>3.0000000000000001E-3</v>
+        <v>1.23E-2</v>
       </c>
       <c r="H325">
         <v>0.30719999999999997</v>
       </c>
       <c r="I325">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J325">
         <v>152.1</v>
@@ -51427,13 +51427,13 @@
         <v>2022</v>
       </c>
       <c r="G326">
-        <v>1.23E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="H326">
         <v>0.30719999999999997</v>
       </c>
       <c r="I326">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J326">
         <v>152.1</v>
@@ -52820,19 +52820,19 @@
         <v>2001</v>
       </c>
       <c r="G349">
-        <v>1.9100000000000002E-2</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="H349">
         <v>0.26880000000000004</v>
       </c>
       <c r="I349">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J349">
         <v>152.1</v>
       </c>
       <c r="K349">
-        <v>8.6399999999999988</v>
+        <v>8.64</v>
       </c>
       <c r="M349">
         <v>54</v>
@@ -52879,19 +52879,19 @@
         <v>2001</v>
       </c>
       <c r="G350">
-        <v>1.1999999999999999E-3</v>
+        <v>1.9100000000000002E-2</v>
       </c>
       <c r="H350">
         <v>0.26880000000000004</v>
       </c>
       <c r="I350">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J350">
         <v>152.1</v>
       </c>
       <c r="K350">
-        <v>8.64</v>
+        <v>8.6399999999999988</v>
       </c>
       <c r="M350">
         <v>54</v>
@@ -52997,10 +52997,10 @@
         <v>2006</v>
       </c>
       <c r="G352">
-        <v>8.0999999999999996E-3</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H352">
-        <v>0.26880000000000009</v>
+        <v>0.26880000000000004</v>
       </c>
       <c r="I352">
         <v>4016.25</v>
@@ -53009,7 +53009,7 @@
         <v>152.1</v>
       </c>
       <c r="K352">
-        <v>8.6400000000000023</v>
+        <v>8.64</v>
       </c>
       <c r="M352">
         <v>50</v>
@@ -53056,10 +53056,10 @@
         <v>2006</v>
       </c>
       <c r="G353">
-        <v>1.7000000000000001E-2</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="H353">
-        <v>0.26880000000000004</v>
+        <v>0.26880000000000009</v>
       </c>
       <c r="I353">
         <v>4016.25</v>
@@ -53068,7 +53068,7 @@
         <v>152.1</v>
       </c>
       <c r="K353">
-        <v>8.64</v>
+        <v>8.6400000000000023</v>
       </c>
       <c r="M353">
         <v>50</v>
@@ -53410,19 +53410,19 @@
         <v>2016</v>
       </c>
       <c r="G359">
-        <v>1.5699999999999999E-2</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="H359">
         <v>0.28799999999999998</v>
       </c>
       <c r="I359">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J359">
-        <v>152.10000000000002</v>
+        <v>152.1</v>
       </c>
       <c r="K359">
-        <v>8.6400000000000023</v>
+        <v>8.64</v>
       </c>
       <c r="M359">
         <v>50</v>
@@ -53469,19 +53469,19 @@
         <v>2016</v>
       </c>
       <c r="G360">
-        <v>2.7000000000000001E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="H360">
         <v>0.28799999999999998</v>
       </c>
       <c r="I360">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J360">
-        <v>152.1</v>
+        <v>152.10000000000002</v>
       </c>
       <c r="K360">
-        <v>8.64</v>
+        <v>8.6400000000000023</v>
       </c>
       <c r="M360">
         <v>50</v>
@@ -53767,7 +53767,7 @@
         <v>1986</v>
       </c>
       <c r="G365">
-        <v>4.2000000000000006E-3</v>
+        <v>0.04</v>
       </c>
       <c r="H365">
         <v>0.23519999999999999</v>
@@ -53829,7 +53829,7 @@
         <v>1986</v>
       </c>
       <c r="G366">
-        <v>0.04</v>
+        <v>4.2000000000000006E-3</v>
       </c>
       <c r="H366">
         <v>0.23519999999999999</v>
@@ -54139,19 +54139,19 @@
         <v>2001</v>
       </c>
       <c r="G371">
-        <v>0.02</v>
+        <v>4.8799999999999996E-2</v>
       </c>
       <c r="H371">
         <v>0.26880000000000004</v>
       </c>
       <c r="I371">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="J371">
         <v>152.1</v>
       </c>
       <c r="K371">
-        <v>8.64</v>
+        <v>8.6400000000000023</v>
       </c>
       <c r="L371">
         <v>0.8</v>
@@ -54201,19 +54201,19 @@
         <v>2001</v>
       </c>
       <c r="G372">
-        <v>4.8799999999999996E-2</v>
+        <v>0.02</v>
       </c>
       <c r="H372">
         <v>0.26880000000000004</v>
       </c>
       <c r="I372">
-        <v>4016.2500000000005</v>
+        <v>4016.25</v>
       </c>
       <c r="J372">
         <v>152.1</v>
       </c>
       <c r="K372">
-        <v>8.6400000000000023</v>
+        <v>8.64</v>
       </c>
       <c r="L372">
         <v>0.8</v>
@@ -57506,7 +57506,7 @@
         <v>2006</v>
       </c>
       <c r="G427">
-        <v>1.9E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H427">
         <v>0.26880000000000004</v>
@@ -57565,7 +57565,7 @@
         <v>2006</v>
       </c>
       <c r="G428">
-        <v>8.0000000000000002E-3</v>
+        <v>1.9E-2</v>
       </c>
       <c r="H428">
         <v>0.26880000000000004</v>
@@ -57683,10 +57683,10 @@
         <v>2008</v>
       </c>
       <c r="G430">
-        <v>8.5199999999999998E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="H430">
-        <v>0.26880000000000004</v>
+        <v>0.26880000000000009</v>
       </c>
       <c r="I430">
         <v>4016.25</v>
@@ -57695,7 +57695,7 @@
         <v>152.1</v>
       </c>
       <c r="K430">
-        <v>8.64</v>
+        <v>8.6400000000000023</v>
       </c>
       <c r="M430">
         <v>50</v>
@@ -57742,10 +57742,10 @@
         <v>2008</v>
       </c>
       <c r="G431">
-        <v>3.2399999999999998E-2</v>
+        <v>8.5199999999999998E-2</v>
       </c>
       <c r="H431">
-        <v>0.26880000000000009</v>
+        <v>0.26880000000000004</v>
       </c>
       <c r="I431">
         <v>4016.25</v>
@@ -57754,7 +57754,7 @@
         <v>152.1</v>
       </c>
       <c r="K431">
-        <v>8.6400000000000023</v>
+        <v>8.64</v>
       </c>
       <c r="M431">
         <v>50</v>
@@ -58096,7 +58096,7 @@
         <v>2013</v>
       </c>
       <c r="G437">
-        <v>2.4E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="H437">
         <v>0.28799999999999998</v>
@@ -58155,7 +58155,7 @@
         <v>2013</v>
       </c>
       <c r="G438">
-        <v>2.5999999999999999E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="H438">
         <v>0.28799999999999998</v>
@@ -58450,7 +58450,7 @@
         <v>2017</v>
       </c>
       <c r="G443">
-        <v>8.0000000000000002E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="H443">
         <v>0.28799999999999998</v>
@@ -58509,7 +58509,7 @@
         <v>2017</v>
       </c>
       <c r="G444">
-        <v>8.5000000000000006E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H444">
         <v>0.28799999999999998</v>
@@ -59052,10 +59052,10 @@
         <v>1994</v>
       </c>
       <c r="G453">
-        <v>2.1000000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="H453">
-        <v>0.24480000000000002</v>
+        <v>0.24479999999999999</v>
       </c>
       <c r="I453">
         <v>4016.25</v>
@@ -59114,10 +59114,10 @@
         <v>1994</v>
       </c>
       <c r="G454">
-        <v>0.01</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H454">
-        <v>0.24479999999999999</v>
+        <v>0.24480000000000002</v>
       </c>
       <c r="I454">
         <v>4016.25</v>
@@ -59610,13 +59610,13 @@
         <v>2008</v>
       </c>
       <c r="G462">
-        <v>0.1787</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="H462">
         <v>0.26880000000000004</v>
       </c>
       <c r="I462">
-        <v>4016.2500000000005</v>
+        <v>4016.25</v>
       </c>
       <c r="J462">
         <v>152.1</v>
@@ -59672,13 +59672,13 @@
         <v>2008</v>
       </c>
       <c r="G463">
-        <v>6.8000000000000005E-2</v>
+        <v>0.1787</v>
       </c>
       <c r="H463">
         <v>0.26880000000000004</v>
       </c>
       <c r="I463">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="J463">
         <v>152.1</v>
@@ -59734,10 +59734,10 @@
         <v>2009</v>
       </c>
       <c r="G464">
-        <v>7.9000000000000001E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="H464">
-        <v>0.26880000000000009</v>
+        <v>0.26880000000000004</v>
       </c>
       <c r="I464">
         <v>4016.25</v>
@@ -59796,10 +59796,10 @@
         <v>2009</v>
       </c>
       <c r="G465">
-        <v>1.2E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="H465">
-        <v>0.26880000000000004</v>
+        <v>0.26880000000000009</v>
       </c>
       <c r="I465">
         <v>4016.25</v>
@@ -59858,13 +59858,13 @@
         <v>2010</v>
       </c>
       <c r="G466">
-        <v>0.3216</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="H466">
         <v>0.26880000000000004</v>
       </c>
       <c r="I466">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J466">
         <v>152.1</v>
@@ -59920,13 +59920,13 @@
         <v>2010</v>
       </c>
       <c r="G467">
-        <v>3.4000000000000002E-2</v>
+        <v>0.3216</v>
       </c>
       <c r="H467">
         <v>0.26880000000000004</v>
       </c>
       <c r="I467">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J467">
         <v>152.1</v>
@@ -60044,7 +60044,7 @@
         <v>2012</v>
       </c>
       <c r="G469">
-        <v>0.14299999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="H469">
         <v>0.28799999999999998</v>
@@ -60106,7 +60106,7 @@
         <v>2012</v>
       </c>
       <c r="G470">
-        <v>0.115</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H470">
         <v>0.28799999999999998</v>
@@ -61098,7 +61098,7 @@
         <v>2028</v>
       </c>
       <c r="G486">
-        <v>0.04</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H486">
         <v>0.30719999999999997</v>
@@ -61160,7 +61160,7 @@
         <v>2028</v>
       </c>
       <c r="G487">
-        <v>2.5000000000000001E-2</v>
+        <v>0.04</v>
       </c>
       <c r="H487">
         <v>0.30719999999999997</v>
@@ -62190,7 +62190,7 @@
         <v>15</v>
       </c>
       <c r="S504" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T504" t="s">
         <v>740</v>
@@ -62249,7 +62249,7 @@
         <v>15</v>
       </c>
       <c r="S505" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T505" t="s">
         <v>740</v>
@@ -62485,7 +62485,7 @@
         <v>15</v>
       </c>
       <c r="S509" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T509" t="s">
         <v>740</v>
@@ -62544,7 +62544,7 @@
         <v>15</v>
       </c>
       <c r="S510" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T510" t="s">
         <v>740</v>
@@ -62662,7 +62662,7 @@
         <v>15</v>
       </c>
       <c r="S512" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T512" t="s">
         <v>740</v>
@@ -62721,7 +62721,7 @@
         <v>15</v>
       </c>
       <c r="S513" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T513" t="s">
         <v>740</v>
@@ -63578,7 +63578,7 @@
         <v>15</v>
       </c>
       <c r="S529" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T529" t="s">
         <v>740</v>
@@ -63640,7 +63640,7 @@
         <v>15</v>
       </c>
       <c r="S530" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T530" t="s">
         <v>740</v>
@@ -63699,7 +63699,7 @@
         <v>15</v>
       </c>
       <c r="S531" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T531" t="s">
         <v>740</v>
@@ -63758,7 +63758,7 @@
         <v>15</v>
       </c>
       <c r="S532" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T532" t="s">
         <v>740</v>
@@ -63820,7 +63820,7 @@
         <v>15</v>
       </c>
       <c r="S533" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T533" t="s">
         <v>740</v>
@@ -63879,7 +63879,7 @@
         <v>15</v>
       </c>
       <c r="S534" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T534" t="s">
         <v>740</v>
@@ -64115,7 +64115,7 @@
         <v>15</v>
       </c>
       <c r="S538" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T538" t="s">
         <v>740</v>
@@ -64174,7 +64174,7 @@
         <v>15</v>
       </c>
       <c r="S539" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T539" t="s">
         <v>740</v>
@@ -64295,7 +64295,7 @@
         <v>15</v>
       </c>
       <c r="S541" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T541" t="s">
         <v>740</v>
@@ -64357,7 +64357,7 @@
         <v>15</v>
       </c>
       <c r="S542" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T542" t="s">
         <v>740</v>
@@ -66954,7 +66954,7 @@
         <v>15</v>
       </c>
       <c r="S585" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T585" t="s">
         <v>740</v>
@@ -67013,7 +67013,7 @@
         <v>15</v>
       </c>
       <c r="S586" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T586" t="s">
         <v>740</v>
@@ -67075,7 +67075,7 @@
         <v>15</v>
       </c>
       <c r="S587" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T587" t="s">
         <v>740</v>
@@ -67125,7 +67125,7 @@
         <v>15</v>
       </c>
       <c r="S588" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T588" t="s">
         <v>740</v>
@@ -67375,7 +67375,7 @@
         <v>15</v>
       </c>
       <c r="S593" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T593" t="s">
         <v>740</v>
@@ -67425,7 +67425,7 @@
         <v>15</v>
       </c>
       <c r="S594" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T594" t="s">
         <v>740</v>
@@ -82947,7 +82947,7 @@
         <v>2025</v>
       </c>
       <c r="G1014">
-        <v>0.28860000000000002</v>
+        <v>0.57679999999999998</v>
       </c>
       <c r="H1014">
         <v>1</v>
@@ -82956,7 +82956,7 @@
         <v>1032.75</v>
       </c>
       <c r="J1014">
-        <v>17.55</v>
+        <v>17.550000000000004</v>
       </c>
       <c r="K1014">
         <v>0</v>
@@ -82965,7 +82965,7 @@
         <v>30</v>
       </c>
       <c r="N1014">
-        <v>0.22298334381027918</v>
+        <v>0.22298334381027923</v>
       </c>
     </row>
     <row r="1015" spans="2:14" x14ac:dyDescent="0.45">
@@ -82985,7 +82985,7 @@
         <v>2025</v>
       </c>
       <c r="G1015">
-        <v>0.57679999999999998</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="H1015">
         <v>1</v>
@@ -82994,7 +82994,7 @@
         <v>1032.75</v>
       </c>
       <c r="J1015">
-        <v>17.550000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="K1015">
         <v>0</v>
@@ -83003,7 +83003,7 @@
         <v>30</v>
       </c>
       <c r="N1015">
-        <v>0.22298334381027923</v>
+        <v>0.22298334381027918</v>
       </c>
     </row>
     <row r="1016" spans="2:14" x14ac:dyDescent="0.45">
@@ -90672,16 +90672,16 @@
         <v>2025</v>
       </c>
       <c r="G1218">
-        <v>5.1299999999999998E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="H1218">
         <v>1</v>
       </c>
       <c r="I1218">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="J1218">
-        <v>39.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="K1218">
         <v>0</v>
@@ -90710,16 +90710,16 @@
         <v>2025</v>
       </c>
       <c r="G1219">
-        <v>2.2800000000000001E-2</v>
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="H1219">
         <v>1</v>
       </c>
       <c r="I1219">
-        <v>1836</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="J1219">
-        <v>46.800000000000004</v>
+        <v>39.6</v>
       </c>
       <c r="K1219">
         <v>0</v>
@@ -91783,7 +91783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05832BB8-34B2-4BC6-B53E-CB60E3254865}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654DD62A-0784-48C4-8D8A-698C2B335039}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids_kan10/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids_kan10/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1C81D25-66E7-4DAD-B08A-5BE6B17F9C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A85C744-3A59-4929-8D08-0D393028065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CEBB5AA6-4D28-4D06-9046-F3B8C26F224A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8E8012C2-6C9F-4184-AC66-BE16B92D995D}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -2283,10 +2283,10 @@
     <t>CHP</t>
   </si>
   <si>
+    <t>Aggregated Plant -- construction -- CHP</t>
+  </si>
+  <si>
     <t>Aggregated Plant -- operating -- CHP (captive)</t>
-  </si>
-  <si>
-    <t>Aggregated Plant -- construction -- CHP</t>
   </si>
   <si>
     <t>Aggregated Plant -- operating -- CHP</t>
@@ -6191,7 +6191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56BCA14-8B19-484D-A8CB-F9CC62931882}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D012250-264F-45B4-A6BA-9CA273D29A8D}">
   <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6578,7 +6578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C236062-3FD3-4218-A0BC-15E4ECF3544D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4532E07A-5A51-43F0-8646-66E6A5936B6E}">
   <dimension ref="B9:V141"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14780,7 +14780,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1751FC-A0D8-4A5C-A4EF-98869A42DC63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A687C2A1-7FD3-4CDE-B123-95F6D596F57D}">
   <dimension ref="B9:W296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22863,7 +22863,7 @@
         <v>2025</v>
       </c>
       <c r="G143">
-        <v>6.2E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="H143">
         <v>0.30719999999999997</v>
@@ -22872,7 +22872,7 @@
         <v>4016.25</v>
       </c>
       <c r="J143">
-        <v>152.10000000000002</v>
+        <v>152.1</v>
       </c>
       <c r="K143">
         <v>8.64</v>
@@ -22922,7 +22922,7 @@
         <v>2025</v>
       </c>
       <c r="G144">
-        <v>4.5999999999999999E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="H144">
         <v>0.30719999999999997</v>
@@ -22931,7 +22931,7 @@
         <v>4016.25</v>
       </c>
       <c r="J144">
-        <v>152.1</v>
+        <v>152.10000000000002</v>
       </c>
       <c r="K144">
         <v>8.64</v>
@@ -32229,7 +32229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8137856-6FBC-4A33-9C85-19BCD8FB8E2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7ECA67-CC0B-4781-87C1-6E41FDE553D2}">
   <dimension ref="B9:W1247"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32409,7 +32409,7 @@
         <v>15</v>
       </c>
       <c r="S12" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T12" t="s">
         <v>740</v>
@@ -32468,7 +32468,7 @@
         <v>15</v>
       </c>
       <c r="S13" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T13" t="s">
         <v>740</v>
@@ -32828,7 +32828,7 @@
         <v>15</v>
       </c>
       <c r="S19" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="T19" t="s">
         <v>740</v>
@@ -32890,7 +32890,7 @@
         <v>15</v>
       </c>
       <c r="S20" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="T20" t="s">
         <v>740</v>
@@ -33014,7 +33014,7 @@
         <v>15</v>
       </c>
       <c r="S22" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T22" t="s">
         <v>740</v>
@@ -33073,7 +33073,7 @@
         <v>15</v>
       </c>
       <c r="S23" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T23" t="s">
         <v>740</v>
@@ -33132,7 +33132,7 @@
         <v>15</v>
       </c>
       <c r="S24" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="T24" t="s">
         <v>740</v>
@@ -33191,7 +33191,7 @@
         <v>15</v>
       </c>
       <c r="S25" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="T25" t="s">
         <v>740</v>
@@ -33309,7 +33309,7 @@
         <v>15</v>
       </c>
       <c r="S27" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T27" t="s">
         <v>740</v>
@@ -33427,7 +33427,7 @@
         <v>15</v>
       </c>
       <c r="S29" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="T29" t="s">
         <v>740</v>
@@ -33486,7 +33486,7 @@
         <v>15</v>
       </c>
       <c r="S30" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="T30" t="s">
         <v>740</v>
@@ -33604,7 +33604,7 @@
         <v>15</v>
       </c>
       <c r="S32" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T32" t="s">
         <v>740</v>
@@ -33722,7 +33722,7 @@
         <v>15</v>
       </c>
       <c r="S34" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T34" t="s">
         <v>740</v>
@@ -33781,7 +33781,7 @@
         <v>15</v>
       </c>
       <c r="S35" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T35" t="s">
         <v>740</v>
@@ -33840,7 +33840,7 @@
         <v>15</v>
       </c>
       <c r="S36" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T36" t="s">
         <v>740</v>
@@ -33964,7 +33964,7 @@
         <v>15</v>
       </c>
       <c r="S38" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T38" t="s">
         <v>740</v>
@@ -34088,7 +34088,7 @@
         <v>15</v>
       </c>
       <c r="S40" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="T40" t="s">
         <v>740</v>
@@ -34150,7 +34150,7 @@
         <v>15</v>
       </c>
       <c r="S41" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="T41" t="s">
         <v>740</v>
@@ -34398,7 +34398,7 @@
         <v>15</v>
       </c>
       <c r="S45" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="T45" t="s">
         <v>740</v>
@@ -34460,7 +34460,7 @@
         <v>15</v>
       </c>
       <c r="S46" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="T46" t="s">
         <v>740</v>
@@ -34646,7 +34646,7 @@
         <v>15</v>
       </c>
       <c r="S49" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T49" t="s">
         <v>740</v>
@@ -34832,7 +34832,7 @@
         <v>15</v>
       </c>
       <c r="S52" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T52" t="s">
         <v>740</v>
@@ -34891,7 +34891,7 @@
         <v>15</v>
       </c>
       <c r="S53" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T53" t="s">
         <v>740</v>
@@ -34950,7 +34950,7 @@
         <v>15</v>
       </c>
       <c r="S54" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T54" t="s">
         <v>740</v>
@@ -35186,7 +35186,7 @@
         <v>15</v>
       </c>
       <c r="S58" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T58" t="s">
         <v>740</v>
@@ -40568,7 +40568,7 @@
         <v>2021</v>
       </c>
       <c r="G148">
-        <v>2.8999999999999998E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="H148">
         <v>0.30719999999999997</v>
@@ -40627,7 +40627,7 @@
         <v>2021</v>
       </c>
       <c r="G149">
-        <v>3.0999999999999999E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="H149">
         <v>0.30719999999999997</v>
@@ -40686,7 +40686,7 @@
         <v>2022</v>
       </c>
       <c r="G150">
-        <v>2.5000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="H150">
         <v>0.30719999999999997</v>
@@ -40745,7 +40745,7 @@
         <v>2022</v>
       </c>
       <c r="G151">
-        <v>1E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="H151">
         <v>0.30719999999999997</v>
@@ -41994,7 +41994,7 @@
         <v>15</v>
       </c>
       <c r="S171" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T171" t="s">
         <v>740</v>
@@ -42236,7 +42236,7 @@
         <v>15</v>
       </c>
       <c r="S175" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T175" t="s">
         <v>740</v>
@@ -42478,7 +42478,7 @@
         <v>15</v>
       </c>
       <c r="S179" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="T179" t="s">
         <v>740</v>
@@ -42540,7 +42540,7 @@
         <v>15</v>
       </c>
       <c r="S180" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="T180" t="s">
         <v>740</v>
@@ -42664,7 +42664,7 @@
         <v>15</v>
       </c>
       <c r="S182" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T182" t="s">
         <v>740</v>
@@ -42850,7 +42850,7 @@
         <v>15</v>
       </c>
       <c r="S185" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="T185" t="s">
         <v>740</v>
@@ -42909,7 +42909,7 @@
         <v>15</v>
       </c>
       <c r="S186" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="T186" t="s">
         <v>740</v>
@@ -43027,7 +43027,7 @@
         <v>15</v>
       </c>
       <c r="S188" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T188" t="s">
         <v>740</v>
@@ -43151,7 +43151,7 @@
         <v>15</v>
       </c>
       <c r="S190" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T190" t="s">
         <v>740</v>
@@ -43213,7 +43213,7 @@
         <v>15</v>
       </c>
       <c r="S191" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T191" t="s">
         <v>740</v>
@@ -43458,7 +43458,7 @@
         <v>15</v>
       </c>
       <c r="S195" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="T195" t="s">
         <v>740</v>
@@ -43582,7 +43582,7 @@
         <v>15</v>
       </c>
       <c r="S197" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="T197" t="s">
         <v>740</v>
@@ -43830,7 +43830,7 @@
         <v>15</v>
       </c>
       <c r="S201" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="T201" t="s">
         <v>740</v>
@@ -49671,7 +49671,7 @@
         <v>2007</v>
       </c>
       <c r="G297">
-        <v>0.04</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="H297">
         <v>0.26880000000000004</v>
@@ -49733,7 +49733,7 @@
         <v>2007</v>
       </c>
       <c r="G298">
-        <v>3.5000000000000003E-2</v>
+        <v>0.04</v>
       </c>
       <c r="H298">
         <v>0.26880000000000004</v>
@@ -49857,10 +49857,10 @@
         <v>2009</v>
       </c>
       <c r="G300">
-        <v>3.5999999999999997E-2</v>
+        <v>2.5499999999999998E-2</v>
       </c>
       <c r="H300">
-        <v>0.26880000000000004</v>
+        <v>0.26880000000000009</v>
       </c>
       <c r="I300">
         <v>4016.25</v>
@@ -49919,10 +49919,10 @@
         <v>2009</v>
       </c>
       <c r="G301">
-        <v>2.5499999999999998E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="H301">
-        <v>0.26880000000000009</v>
+        <v>0.26880000000000004</v>
       </c>
       <c r="I301">
         <v>4016.25</v>
@@ -51368,13 +51368,13 @@
         <v>2022</v>
       </c>
       <c r="G325">
-        <v>1.23E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="H325">
         <v>0.30719999999999997</v>
       </c>
       <c r="I325">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J325">
         <v>152.1</v>
@@ -51427,13 +51427,13 @@
         <v>2022</v>
       </c>
       <c r="G326">
-        <v>3.0000000000000001E-3</v>
+        <v>1.23E-2</v>
       </c>
       <c r="H326">
         <v>0.30719999999999997</v>
       </c>
       <c r="I326">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J326">
         <v>152.1</v>
@@ -52702,16 +52702,16 @@
         <v>2000</v>
       </c>
       <c r="G347">
-        <v>5.4000000000000003E-3</v>
+        <v>4.7E-2</v>
       </c>
       <c r="H347">
         <v>0.24479999999999999</v>
       </c>
       <c r="I347">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J347">
-        <v>152.09999999999997</v>
+        <v>152.1</v>
       </c>
       <c r="K347">
         <v>8.64</v>
@@ -52761,16 +52761,16 @@
         <v>2000</v>
       </c>
       <c r="G348">
-        <v>4.7E-2</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="H348">
         <v>0.24479999999999999</v>
       </c>
       <c r="I348">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J348">
-        <v>152.1</v>
+        <v>152.09999999999997</v>
       </c>
       <c r="K348">
         <v>8.64</v>
@@ -52820,19 +52820,19 @@
         <v>2001</v>
       </c>
       <c r="G349">
-        <v>1.1999999999999999E-3</v>
+        <v>1.9100000000000002E-2</v>
       </c>
       <c r="H349">
         <v>0.26880000000000004</v>
       </c>
       <c r="I349">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J349">
         <v>152.1</v>
       </c>
       <c r="K349">
-        <v>8.64</v>
+        <v>8.6399999999999988</v>
       </c>
       <c r="M349">
         <v>54</v>
@@ -52879,19 +52879,19 @@
         <v>2001</v>
       </c>
       <c r="G350">
-        <v>1.9100000000000002E-2</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="H350">
         <v>0.26880000000000004</v>
       </c>
       <c r="I350">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J350">
         <v>152.1</v>
       </c>
       <c r="K350">
-        <v>8.6399999999999988</v>
+        <v>8.64</v>
       </c>
       <c r="M350">
         <v>54</v>
@@ -53115,7 +53115,7 @@
         <v>2008</v>
       </c>
       <c r="G354">
-        <v>6.7000000000000002E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="H354">
         <v>0.26880000000000004</v>
@@ -53174,7 +53174,7 @@
         <v>2008</v>
       </c>
       <c r="G355">
-        <v>3.0000000000000001E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="H355">
         <v>0.26880000000000004</v>
@@ -53410,19 +53410,19 @@
         <v>2016</v>
       </c>
       <c r="G359">
-        <v>2.7000000000000001E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="H359">
         <v>0.28799999999999998</v>
       </c>
       <c r="I359">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J359">
-        <v>152.1</v>
+        <v>152.10000000000002</v>
       </c>
       <c r="K359">
-        <v>8.64</v>
+        <v>8.6400000000000023</v>
       </c>
       <c r="M359">
         <v>50</v>
@@ -53469,19 +53469,19 @@
         <v>2016</v>
       </c>
       <c r="G360">
-        <v>1.5699999999999999E-2</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="H360">
         <v>0.28799999999999998</v>
       </c>
       <c r="I360">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J360">
-        <v>152.10000000000002</v>
+        <v>152.1</v>
       </c>
       <c r="K360">
-        <v>8.6400000000000023</v>
+        <v>8.64</v>
       </c>
       <c r="M360">
         <v>50</v>
@@ -54139,19 +54139,19 @@
         <v>2001</v>
       </c>
       <c r="G371">
-        <v>4.8799999999999996E-2</v>
+        <v>0.02</v>
       </c>
       <c r="H371">
         <v>0.26880000000000004</v>
       </c>
       <c r="I371">
-        <v>4016.2500000000005</v>
+        <v>4016.25</v>
       </c>
       <c r="J371">
         <v>152.1</v>
       </c>
       <c r="K371">
-        <v>8.6400000000000023</v>
+        <v>8.64</v>
       </c>
       <c r="L371">
         <v>0.8</v>
@@ -54201,19 +54201,19 @@
         <v>2001</v>
       </c>
       <c r="G372">
-        <v>0.02</v>
+        <v>4.8799999999999996E-2</v>
       </c>
       <c r="H372">
         <v>0.26880000000000004</v>
       </c>
       <c r="I372">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="J372">
         <v>152.1</v>
       </c>
       <c r="K372">
-        <v>8.64</v>
+        <v>8.6400000000000023</v>
       </c>
       <c r="L372">
         <v>0.8</v>
@@ -56084,7 +56084,7 @@
         <v>2015</v>
       </c>
       <c r="G403">
-        <v>5.7999999999999996E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="H403">
         <v>0.28799999999999998</v>
@@ -56143,7 +56143,7 @@
         <v>2015</v>
       </c>
       <c r="G404">
-        <v>1E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="H404">
         <v>0.28799999999999998</v>
@@ -56503,10 +56503,10 @@
         <v>2028</v>
       </c>
       <c r="G410">
-        <v>5.7000000000000002E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="H410">
-        <v>0.30719999999999997</v>
+        <v>0.30720000000000003</v>
       </c>
       <c r="I410">
         <v>4016.25</v>
@@ -56562,10 +56562,10 @@
         <v>2028</v>
       </c>
       <c r="G411">
-        <v>3.8E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="H411">
-        <v>0.30720000000000003</v>
+        <v>0.30719999999999997</v>
       </c>
       <c r="I411">
         <v>4016.25</v>
@@ -57506,7 +57506,7 @@
         <v>2006</v>
       </c>
       <c r="G427">
-        <v>8.0000000000000002E-3</v>
+        <v>1.9E-2</v>
       </c>
       <c r="H427">
         <v>0.26880000000000004</v>
@@ -57565,7 +57565,7 @@
         <v>2006</v>
       </c>
       <c r="G428">
-        <v>1.9E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H428">
         <v>0.26880000000000004</v>
@@ -57860,7 +57860,7 @@
         <v>2010</v>
       </c>
       <c r="G433">
-        <v>8.4000000000000012E-3</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H433">
         <v>0.26880000000000004</v>
@@ -57869,7 +57869,7 @@
         <v>4016.25</v>
       </c>
       <c r="J433">
-        <v>152.09999999999997</v>
+        <v>152.1</v>
       </c>
       <c r="K433">
         <v>8.64</v>
@@ -57919,7 +57919,7 @@
         <v>2010</v>
       </c>
       <c r="G434">
-        <v>4.4999999999999998E-2</v>
+        <v>8.4000000000000012E-3</v>
       </c>
       <c r="H434">
         <v>0.26880000000000004</v>
@@ -57928,7 +57928,7 @@
         <v>4016.25</v>
       </c>
       <c r="J434">
-        <v>152.1</v>
+        <v>152.09999999999997</v>
       </c>
       <c r="K434">
         <v>8.64</v>
@@ -58273,13 +58273,13 @@
         <v>2015</v>
       </c>
       <c r="G440">
-        <v>1.4100000000000001E-2</v>
+        <v>2.87E-2</v>
       </c>
       <c r="H440">
         <v>0.28799999999999998</v>
       </c>
       <c r="I440">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J440">
         <v>152.1</v>
@@ -58332,13 +58332,13 @@
         <v>2015</v>
       </c>
       <c r="G441">
-        <v>2.87E-2</v>
+        <v>1.4100000000000001E-2</v>
       </c>
       <c r="H441">
         <v>0.28799999999999998</v>
       </c>
       <c r="I441">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J441">
         <v>152.1</v>
@@ -58450,7 +58450,7 @@
         <v>2017</v>
       </c>
       <c r="G443">
-        <v>8.5000000000000006E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="H443">
         <v>0.28799999999999998</v>
@@ -58509,7 +58509,7 @@
         <v>2017</v>
       </c>
       <c r="G444">
-        <v>8.0000000000000002E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="H444">
         <v>0.28799999999999998</v>
@@ -59052,10 +59052,10 @@
         <v>1994</v>
       </c>
       <c r="G453">
-        <v>0.01</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H453">
-        <v>0.24479999999999999</v>
+        <v>0.24480000000000002</v>
       </c>
       <c r="I453">
         <v>4016.25</v>
@@ -59114,10 +59114,10 @@
         <v>1994</v>
       </c>
       <c r="G454">
-        <v>2.1000000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="H454">
-        <v>0.24480000000000002</v>
+        <v>0.24479999999999999</v>
       </c>
       <c r="I454">
         <v>4016.25</v>
@@ -59300,7 +59300,7 @@
         <v>2002</v>
       </c>
       <c r="G457">
-        <v>3.5499999999999997E-2</v>
+        <v>0.126</v>
       </c>
       <c r="H457">
         <v>0.26880000000000004</v>
@@ -59309,7 +59309,7 @@
         <v>4016.25</v>
       </c>
       <c r="J457">
-        <v>152.09999999999997</v>
+        <v>152.1</v>
       </c>
       <c r="K457">
         <v>8.64</v>
@@ -59362,7 +59362,7 @@
         <v>2002</v>
       </c>
       <c r="G458">
-        <v>0.126</v>
+        <v>3.5499999999999997E-2</v>
       </c>
       <c r="H458">
         <v>0.26880000000000004</v>
@@ -59371,7 +59371,7 @@
         <v>4016.25</v>
       </c>
       <c r="J458">
-        <v>152.1</v>
+        <v>152.09999999999997</v>
       </c>
       <c r="K458">
         <v>8.64</v>
@@ -59858,13 +59858,13 @@
         <v>2010</v>
       </c>
       <c r="G466">
-        <v>3.4000000000000002E-2</v>
+        <v>0.3216</v>
       </c>
       <c r="H466">
         <v>0.26880000000000004</v>
       </c>
       <c r="I466">
-        <v>4016.25</v>
+        <v>4016.2499999999995</v>
       </c>
       <c r="J466">
         <v>152.1</v>
@@ -59920,13 +59920,13 @@
         <v>2010</v>
       </c>
       <c r="G467">
-        <v>0.3216</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="H467">
         <v>0.26880000000000004</v>
       </c>
       <c r="I467">
-        <v>4016.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="J467">
         <v>152.1</v>
@@ -60168,10 +60168,10 @@
         <v>2013</v>
       </c>
       <c r="G471">
-        <v>0.254</v>
+        <v>0.185</v>
       </c>
       <c r="H471">
-        <v>0.28799999999999998</v>
+        <v>0.28800000000000003</v>
       </c>
       <c r="I471">
         <v>4016.25</v>
@@ -60180,7 +60180,7 @@
         <v>152.1</v>
       </c>
       <c r="K471">
-        <v>8.6400000000000023</v>
+        <v>8.64</v>
       </c>
       <c r="L471">
         <v>0.8</v>
@@ -60230,10 +60230,10 @@
         <v>2013</v>
       </c>
       <c r="G472">
-        <v>0.185</v>
+        <v>0.254</v>
       </c>
       <c r="H472">
-        <v>0.28800000000000003</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="I472">
         <v>4016.25</v>
@@ -60242,7 +60242,7 @@
         <v>152.1</v>
       </c>
       <c r="K472">
-        <v>8.64</v>
+        <v>8.6400000000000023</v>
       </c>
       <c r="L472">
         <v>0.8</v>
@@ -60292,10 +60292,10 @@
         <v>2014</v>
       </c>
       <c r="G473">
-        <v>9.0999999999999998E-2</v>
+        <v>4.8399999999999999E-2</v>
       </c>
       <c r="H473">
-        <v>0.28799999999999992</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="I473">
         <v>4016.25</v>
@@ -60354,10 +60354,10 @@
         <v>2014</v>
       </c>
       <c r="G474">
-        <v>4.8399999999999999E-2</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="H474">
-        <v>0.28799999999999998</v>
+        <v>0.28799999999999992</v>
       </c>
       <c r="I474">
         <v>4016.25</v>
@@ -60416,19 +60416,19 @@
         <v>2015</v>
       </c>
       <c r="G475">
-        <v>1.2E-2</v>
+        <v>0.17579999999999998</v>
       </c>
       <c r="H475">
-        <v>0.28799999999999998</v>
+        <v>0.28800000000000003</v>
       </c>
       <c r="I475">
-        <v>4016.25</v>
+        <v>4016.2500000000005</v>
       </c>
       <c r="J475">
-        <v>152.1</v>
+        <v>152.10000000000002</v>
       </c>
       <c r="K475">
-        <v>8.64</v>
+        <v>8.6400000000000023</v>
       </c>
       <c r="L475">
         <v>0.8</v>
@@ -60478,19 +60478,19 @@
         <v>2015</v>
       </c>
       <c r="G476">
-        <v>0.17579999999999998</v>
+        <v>1.2E-2</v>
       </c>
       <c r="H476">
-        <v>0.28800000000000003</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="I476">
-        <v>4016.2500000000005</v>
+        <v>4016.25</v>
       </c>
       <c r="J476">
-        <v>152.10000000000002</v>
+        <v>152.1</v>
       </c>
       <c r="K476">
-        <v>8.6400000000000023</v>
+        <v>8.64</v>
       </c>
       <c r="L476">
         <v>0.8</v>
@@ -62485,7 +62485,7 @@
         <v>15</v>
       </c>
       <c r="S509" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T509" t="s">
         <v>740</v>
@@ -62544,7 +62544,7 @@
         <v>15</v>
       </c>
       <c r="S510" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T510" t="s">
         <v>740</v>
@@ -62662,7 +62662,7 @@
         <v>15</v>
       </c>
       <c r="S512" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T512" t="s">
         <v>740</v>
@@ -62721,7 +62721,7 @@
         <v>15</v>
       </c>
       <c r="S513" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T513" t="s">
         <v>740</v>
@@ -63221,7 +63221,7 @@
         <v>15</v>
       </c>
       <c r="S523" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T523" t="s">
         <v>740</v>
@@ -63271,7 +63271,7 @@
         <v>15</v>
       </c>
       <c r="S524" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T524" t="s">
         <v>740</v>
@@ -63578,7 +63578,7 @@
         <v>15</v>
       </c>
       <c r="S529" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T529" t="s">
         <v>740</v>
@@ -63640,7 +63640,7 @@
         <v>15</v>
       </c>
       <c r="S530" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T530" t="s">
         <v>740</v>
@@ -63699,7 +63699,7 @@
         <v>15</v>
       </c>
       <c r="S531" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T531" t="s">
         <v>740</v>
@@ -63758,7 +63758,7 @@
         <v>15</v>
       </c>
       <c r="S532" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T532" t="s">
         <v>740</v>
@@ -64115,7 +64115,7 @@
         <v>15</v>
       </c>
       <c r="S538" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T538" t="s">
         <v>740</v>
@@ -64174,7 +64174,7 @@
         <v>15</v>
       </c>
       <c r="S539" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T539" t="s">
         <v>740</v>
@@ -64295,7 +64295,7 @@
         <v>15</v>
       </c>
       <c r="S541" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T541" t="s">
         <v>740</v>
@@ -64357,7 +64357,7 @@
         <v>15</v>
       </c>
       <c r="S542" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T542" t="s">
         <v>740</v>
@@ -66777,7 +66777,7 @@
         <v>15</v>
       </c>
       <c r="S582" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T582" t="s">
         <v>740</v>
@@ -66836,7 +66836,7 @@
         <v>15</v>
       </c>
       <c r="S583" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T583" t="s">
         <v>740</v>
@@ -66954,7 +66954,7 @@
         <v>15</v>
       </c>
       <c r="S585" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="T585" t="s">
         <v>740</v>
@@ -67013,7 +67013,7 @@
         <v>15</v>
       </c>
       <c r="S586" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="T586" t="s">
         <v>740</v>
@@ -91783,7 +91783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{654DD62A-0784-48C4-8D8A-698C2B335039}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5337FC3A-3212-4CBC-974C-CDEDC34C55DC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
